--- a/火山引擎报价单-北京-云数据库MySQL5.7-4核8G-100G.xlsx
+++ b/火山引擎报价单-北京-云数据库MySQL5.7-4核8G-100G.xlsx
@@ -1548,7 +1548,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="19">
+    <row r="4" ht="120" customHeight="1" s="19">
       <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
@@ -1564,19 +1564,22 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>版本：MySQL 5.7
-架构：高可用版（双节点）
-规格：通用规格 4核8G（rds.mysql.c.s.4c8g）
-存储：高性能云盘 200G（双节点，100G/节点）</t>
+          <t>兼容版本：MySQL 5.7
+引擎类型：InnoDB
+实例类型：双节点
+规格类型：通用规格
+存储类型：本地SSD盘
+节点规格：主节点 4核8G（rds.mysql.d1.n.4c8g）
+存储空间：100G</t>
         </is>
       </c>
       <c r="E4" s="22">
-        <f>7200+2400</f>
-        <v>9600</v>
+        <f>7176+3864</f>
+        <v>11040</v>
         <v/>
       </c>
       <c r="F4" s="22" t="n">
-        <v>7200</v>
+        <v>7176</v>
       </c>
       <c r="G4" s="10" t="n"/>
     </row>
@@ -1591,12 +1594,12 @@
       <c r="D5" s="21" t="n"/>
       <c r="E5" s="24">
         <f>SUM(E4:E4)</f>
-        <v>9600</v>
+        <v>11040</v>
         <v/>
       </c>
       <c r="F5" s="25">
         <f>SUM(F4:F4)</f>
-        <v>7200</v>
+        <v>7176</v>
         <v/>
       </c>
       <c r="G5" s="27" t="inlineStr">
